--- a/scripts/empresasparceiras.xlsx
+++ b/scripts/empresasparceiras.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\tr.alienigenaV5-main\scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6C33534D-F46C-4EE5-B717-46D804DE823D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1794DF4B-9B84-4E36-9EA1-A80722615AFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{85DC10FC-BDBB-4A78-BCB2-4C685732CF65}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>Empresa</t>
   </si>
@@ -163,12 +163,6 @@
   </si>
   <si>
     <t>(88) 9612-1572</t>
-  </si>
-  <si>
-    <t>Scoria</t>
-  </si>
-  <si>
-    <t>Empresa parceira cadastrada no portal, mas a atividade e os contatos ainda precisam ser confirmados para descrever corretamente o serviço.</t>
   </si>
   <si>
     <t>SEST SENAT Sobral</t>
@@ -595,7 +589,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{362F7BF9-CB24-46D1-98C7-59BE3B85FFF6}">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40.21875" style="1" bestFit="1" customWidth="1"/>
@@ -631,7 +625,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -682,10 +676,10 @@
         <v>19</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>20</v>
@@ -736,7 +730,7 @@
         <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
@@ -781,7 +775,7 @@
         <v>88988922392</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
@@ -802,73 +796,65 @@
       <c r="B13" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="C14" s="1">
+        <v>88994371661</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1">
-        <v>88994371661</v>
+        <v>56</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>57</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
+      </c>
+      <c r="C16" s="1">
+        <v>88981543064</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B17" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="C17" s="1">
-        <v>88981543064</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
